--- a/artfynd/A 18328-2024 artfynd.xlsx
+++ b/artfynd/A 18328-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118095215</v>
+        <v>118095336</v>
       </c>
       <c r="B2" t="n">
-        <v>79523</v>
+        <v>57304</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229497</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Björnemyren (Björnemyren), Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>316457</v>
+        <v>316431</v>
       </c>
       <c r="R2" t="n">
-        <v>6546993</v>
+        <v>6547005</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118095336</v>
+        <v>118095300</v>
       </c>
       <c r="B3" t="n">
-        <v>57304</v>
+        <v>57288</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,16 +808,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -821,21 +826,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björnemyren (Björnemyren), Dls</t>
+          <t>Björnemyrfjället (Björnemyrfjället), Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>316431</v>
+        <v>316450</v>
       </c>
       <c r="R3" t="n">
-        <v>6547005</v>
+        <v>6546979</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack i tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118095300</v>
+        <v>118095215</v>
       </c>
       <c r="B4" t="n">
-        <v>57288</v>
+        <v>79523</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,38 +921,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björnemyrfjället (Björnemyrfjället), Dls</t>
+          <t>Björnemyren (Björnemyren), Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>316450</v>
+        <v>316457</v>
       </c>
       <c r="R4" t="n">
-        <v>6546979</v>
+        <v>6546993</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack i tall</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 18328-2024 artfynd.xlsx
+++ b/artfynd/A 18328-2024 artfynd.xlsx
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118095545</v>
+        <v>118095336</v>
       </c>
       <c r="B2" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -716,14 +711,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björnemyrfjället (Björnemyrfjället), Dls</t>
+          <t>Björnemyren, Björnemyren, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>316418</v>
+        <v>316431</v>
       </c>
       <c r="R2" t="n">
-        <v>6546986</v>
+        <v>6547005</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,32 +787,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118095300</v>
+        <v>118095545</v>
       </c>
       <c r="B3" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -826,16 +816,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björnemyrfjället (Björnemyrfjället), Dls</t>
+          <t>Björnemyrfjället, Björnemyrfjället, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>316450</v>
+        <v>316418</v>
       </c>
       <c r="R3" t="n">
-        <v>6546979</v>
+        <v>6546986</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack i tall</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,50 +899,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118095215</v>
+        <v>118095300</v>
       </c>
       <c r="B4" t="n">
-        <v>79525</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björnemyren (Björnemyren), Dls</t>
+          <t>Björnemyrfjället, Björnemyrfjället, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>316457</v>
+        <v>316450</v>
       </c>
       <c r="R4" t="n">
-        <v>6546993</v>
+        <v>6546979</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack i tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,55 +1011,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118095336</v>
+        <v>118095215</v>
       </c>
       <c r="B5" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>229497</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björnemyren (Björnemyren), Dls</t>
+          <t>Björnemyren, Björnemyren, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>316431</v>
+        <v>316457</v>
       </c>
       <c r="R5" t="n">
-        <v>6547005</v>
+        <v>6546993</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 18328-2024 artfynd.xlsx
+++ b/artfynd/A 18328-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118095336</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118095545</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118095300</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,8 +1135,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118095215</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>